--- a/samples/L_应付职工薪酬明细表.xlsx
+++ b/samples/L_应付职工薪酬明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,197 +438,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>期初余额</t>
+          <t>人员数量</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>本期计提</t>
+          <t>工资计提</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>本期支付</t>
+          <t>社保单位</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>公积金单位</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>个税代扣</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>实发工资</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>期末余额</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>计提基数</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>计提比例</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>生产车间</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>6100000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>85人</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>714000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>420000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>168000</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4958000</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>养老保险</t>
+          <t>研发中心</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>960000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>970000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>工资总额</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>646000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>380000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>152000</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4474000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>医疗保险</t>
+          <t>销售部门</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>306000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2118000</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>480000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>490000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>工资总额</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>住房公积金</t>
+          <t>管理部门</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1060000</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>1070000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>110000</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>工资总额</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>255000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1765000</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>年终奖</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>102000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>706000</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>11900000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2023000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1190000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>476000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>14017000</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>350000</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>年终奖未计提70,000元，需补提!</t>
         </is>
       </c>
     </row>
